--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1503-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1503-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D9E0CAE-191B-47D0-9AE5-84506B2D3462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45E2E762-9B80-4F99-93E3-3A0C0A85BD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{51343401-0FCD-4AC4-9569-A1024D7B88DD}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{EA20AA07-BC45-4FA4-AAF4-6D545A85000F}"/>
   </bookViews>
   <sheets>
     <sheet name="1503-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1604,28 +1604,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB09A81F-372C-43DC-A096-BCF7A69D7690}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8094045-D838-4F74-98E0-D1357F3A6639}">
   <dimension ref="A1:X53"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1659,7 +1658,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1695,7 +1694,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1747,7 +1746,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1815,7 +1814,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1887,7 +1886,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1959,7 +1958,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2031,7 +2030,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2103,7 +2102,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2175,7 +2174,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2247,7 +2246,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2319,7 +2318,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2391,7 +2390,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2463,7 +2462,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2015</v>
       </c>
@@ -2535,7 +2534,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2014</v>
       </c>
@@ -2607,7 +2606,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2013</v>
       </c>
@@ -2679,7 +2678,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2012</v>
       </c>
@@ -2751,7 +2750,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2011</v>
       </c>
@@ -2823,7 +2822,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2010</v>
       </c>
@@ -2895,7 +2894,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2009</v>
       </c>
@@ -2967,7 +2966,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2008</v>
       </c>
@@ -3039,7 +3038,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <v>2007</v>
       </c>
@@ -3111,7 +3110,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2006</v>
       </c>
@@ -3183,7 +3182,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>2005</v>
       </c>
@@ -3255,7 +3254,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2004</v>
       </c>
@@ -3327,7 +3326,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <v>2003</v>
       </c>
@@ -3399,7 +3398,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2002</v>
       </c>
@@ -3471,7 +3470,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2001</v>
       </c>
@@ -3543,7 +3542,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2000</v>
       </c>
@@ -3615,7 +3614,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>1999</v>
       </c>
@@ -3687,7 +3686,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>1998</v>
       </c>
@@ -3759,7 +3758,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>1997</v>
       </c>
@@ -3831,7 +3830,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="42">
         <v>1996</v>
       </c>
@@ -3903,7 +3902,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="44"/>
       <c r="B34" s="45"/>
       <c r="C34" s="19" t="s">
@@ -3931,7 +3930,7 @@
       <c r="W34" s="51"/>
       <c r="X34" s="47"/>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="52">
         <v>1995</v>
       </c>
@@ -4003,7 +4002,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="54"/>
       <c r="B36" s="55"/>
       <c r="C36" s="21" t="s">
@@ -4031,7 +4030,7 @@
       <c r="W36" s="61"/>
       <c r="X36" s="57"/>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>1994</v>
       </c>
@@ -4103,7 +4102,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="52">
         <v>1993</v>
       </c>
@@ -4175,7 +4174,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="54"/>
       <c r="B39" s="55"/>
       <c r="C39" s="21" t="s">
@@ -4203,7 +4202,7 @@
       <c r="W39" s="61"/>
       <c r="X39" s="57"/>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="42">
         <v>1992</v>
       </c>
@@ -4275,7 +4274,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="44"/>
       <c r="B41" s="45"/>
       <c r="C41" s="19" t="s">
@@ -4303,7 +4302,7 @@
       <c r="W41" s="51"/>
       <c r="X41" s="47"/>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="52">
         <v>1991</v>
       </c>
@@ -4375,7 +4374,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="54"/>
       <c r="B43" s="55"/>
       <c r="C43" s="21" t="s">
@@ -4403,7 +4402,7 @@
       <c r="W43" s="61"/>
       <c r="X43" s="57"/>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="42">
         <v>1990</v>
       </c>
@@ -4475,7 +4474,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="44"/>
       <c r="B45" s="45"/>
       <c r="C45" s="19" t="s">
@@ -4503,7 +4502,7 @@
       <c r="W45" s="51"/>
       <c r="X45" s="47"/>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="40">
         <v>1989</v>
       </c>
@@ -4575,7 +4574,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>1988</v>
       </c>
@@ -4647,7 +4646,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="40">
         <v>1987</v>
       </c>
@@ -4719,7 +4718,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="38">
         <v>1986</v>
       </c>
@@ -4791,7 +4790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="40">
         <v>1985</v>
       </c>
@@ -4863,7 +4862,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="38">
         <v>1984</v>
       </c>
@@ -4935,7 +4934,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="40">
         <v>1983</v>
       </c>
@@ -5007,7 +5006,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="38" t="s">
         <v>69</v>
       </c>
